--- a/data/worksheet_database.xlsx
+++ b/data/worksheet_database.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14400" windowHeight="12450" activeTab="2"/>
+    <workbookView windowWidth="14400" windowHeight="12450" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Words" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="261">
   <si>
     <t>ID</t>
   </si>
@@ -566,10 +566,10 @@
     <t>Ayam</t>
   </si>
   <si>
-    <t>Egg</t>
-  </si>
-  <si>
-    <t>Telur</t>
+    <t>Monkey</t>
+  </si>
+  <si>
+    <t>Monyet</t>
   </si>
   <si>
     <t>cute cartoon chicken holding a big egg, thick dark-navy outline, flat bright colors, plain white background, friendly smile, no text</t>
@@ -578,7 +578,7 @@
     <t>Lebah</t>
   </si>
   <si>
-    <t>Madu</t>
+    <t>Panda</t>
   </si>
   <si>
     <t>cute cartoon bee next to a honey jar, thick dark-navy outline, flat bright colors, plain white background, friendly smile, no text</t>
@@ -587,148 +587,178 @@
     <t>Sapi</t>
   </si>
   <si>
+    <t>Penguin</t>
+  </si>
+  <si>
+    <t>Pinguin</t>
+  </si>
+  <si>
+    <t>cute cartoon cow face beside a milk carton, thick dark-navy outline, flat bright colors, plain white background, friendly smile, no text</t>
+  </si>
+  <si>
+    <t>Gajah</t>
+  </si>
+  <si>
+    <t>Babi</t>
+  </si>
+  <si>
+    <t>cute cartoon fluffy sheep beside a ball of yarn, thick dark-navy outline, flat bright colors, plain white background, friendly smile, no text</t>
+  </si>
+  <si>
+    <t>Plants &amp; Fruits</t>
+  </si>
+  <si>
+    <t>Shark</t>
+  </si>
+  <si>
+    <t>Hiu</t>
+  </si>
+  <si>
+    <t>Puppy</t>
+  </si>
+  <si>
+    <t>Anjing</t>
+  </si>
+  <si>
+    <t>cute cartoon apple tree and one big red apple, thick dark-navy outline, flat bright colors, plain white background, friendly smile, no text</t>
+  </si>
+  <si>
+    <t>Letter</t>
+  </si>
+  <si>
+    <t>Ant</t>
+  </si>
+  <si>
+    <t>Semut</t>
+  </si>
+  <si>
+    <t>Dolphin</t>
+  </si>
+  <si>
+    <t>Lumba Lumba</t>
+  </si>
+  <si>
+    <t>cute cartoon egg, thick dark-navy outline, flat bright colors, plain white background, friendly smile, no text</t>
+  </si>
+  <si>
+    <t>Ikan</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>Giraffe</t>
+  </si>
+  <si>
+    <t>Jerapah</t>
+  </si>
+  <si>
+    <t>cute cartoon grapes, thick dark-navy outline, flat bright colors, plain white background, friendly smile, no text</t>
+  </si>
+  <si>
+    <t>Horse</t>
+  </si>
+  <si>
+    <t>Kuda</t>
+  </si>
+  <si>
+    <t>Kangaro</t>
+  </si>
+  <si>
+    <t>Kangguru</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>Lion</t>
+  </si>
+  <si>
+    <t>Singa</t>
+  </si>
+  <si>
+    <t>cute cartoon jellyfish, thick dark-navy outline, flat bright colors, plain white background, friendly smile, no text</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>cute cartoon kite, thick dark-navy outline, flat bright colors, plain white background, friendly smile, no text</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>Lemon</t>
+  </si>
+  <si>
+    <t>cute cartoon lemon, thick dark-navy outline, flat bright colors, plain white background, friendly smile, no text</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
     <t>Milk</t>
   </si>
   <si>
     <t>Susu</t>
   </si>
   <si>
-    <t>cute cartoon cow face beside a milk carton, thick dark-navy outline, flat bright colors, plain white background, friendly smile, no text</t>
+    <t>cute cartoon milk, thick dark-navy outline, flat bright colors, plain white background, friendly smile, no text</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Nest</t>
+  </si>
+  <si>
+    <t>Sarang</t>
+  </si>
+  <si>
+    <t>cute cartoon nest, thick dark-navy outline, flat bright colors, plain white background, friendly smile, no text</t>
+  </si>
+  <si>
+    <t>Jeruk</t>
+  </si>
+  <si>
+    <t>Ratu</t>
+  </si>
+  <si>
+    <t>Kelinci</t>
   </si>
   <si>
     <t>Domba</t>
   </si>
   <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>Tree</t>
+  </si>
+  <si>
+    <t>Pohon</t>
+  </si>
+  <si>
+    <t>cute cartoon tree, thick dark-navy outline, flat bright colors, plain white background, friendly smile, no text</t>
+  </si>
+  <si>
+    <t>Payung</t>
+  </si>
+  <si>
+    <t>Van</t>
+  </si>
+  <si>
+    <t>Mobil van</t>
+  </si>
+  <si>
+    <t>cute cartoon van, thick dark-navy outline, flat bright colors, plain white background, friendly smile, no text</t>
+  </si>
+  <si>
     <t>Wool</t>
   </si>
   <si>
     <t>Wol</t>
-  </si>
-  <si>
-    <t>cute cartoon fluffy sheep beside a ball of yarn, thick dark-navy outline, flat bright colors, plain white background, friendly smile, no text</t>
-  </si>
-  <si>
-    <t>Plants &amp; Fruits</t>
-  </si>
-  <si>
-    <t>Tree</t>
-  </si>
-  <si>
-    <t>Pohon</t>
-  </si>
-  <si>
-    <t>Apel</t>
-  </si>
-  <si>
-    <t>cute cartoon apple tree and one big red apple, thick dark-navy outline, flat bright colors, plain white background, friendly smile, no text</t>
-  </si>
-  <si>
-    <t>Letter</t>
-  </si>
-  <si>
-    <t>Bebek</t>
-  </si>
-  <si>
-    <t>cute cartoon egg, thick dark-navy outline, flat bright colors, plain white background, friendly smile, no text</t>
-  </si>
-  <si>
-    <t>Ikan</t>
-  </si>
-  <si>
-    <t>G</t>
-  </si>
-  <si>
-    <t>Grapes</t>
-  </si>
-  <si>
-    <t>Anggur</t>
-  </si>
-  <si>
-    <t>cute cartoon grapes, thick dark-navy outline, flat bright colors, plain white background, friendly smile, no text</t>
-  </si>
-  <si>
-    <t>Es krim</t>
-  </si>
-  <si>
-    <t>J</t>
-  </si>
-  <si>
-    <t>Jellyfish</t>
-  </si>
-  <si>
-    <t>Ubur-ubur</t>
-  </si>
-  <si>
-    <t>cute cartoon jellyfish, thick dark-navy outline, flat bright colors, plain white background, friendly smile, no text</t>
-  </si>
-  <si>
-    <t>K</t>
-  </si>
-  <si>
-    <t>Kite</t>
-  </si>
-  <si>
-    <t>Layang-layang</t>
-  </si>
-  <si>
-    <t>cute cartoon kite, thick dark-navy outline, flat bright colors, plain white background, friendly smile, no text</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>Lemon</t>
-  </si>
-  <si>
-    <t>cute cartoon lemon, thick dark-navy outline, flat bright colors, plain white background, friendly smile, no text</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>cute cartoon milk, thick dark-navy outline, flat bright colors, plain white background, friendly smile, no text</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>Nest</t>
-  </si>
-  <si>
-    <t>Sarang</t>
-  </si>
-  <si>
-    <t>cute cartoon nest, thick dark-navy outline, flat bright colors, plain white background, friendly smile, no text</t>
-  </si>
-  <si>
-    <t>Jeruk</t>
-  </si>
-  <si>
-    <t>Babi</t>
-  </si>
-  <si>
-    <t>Ratu</t>
-  </si>
-  <si>
-    <t>Kelinci</t>
-  </si>
-  <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>cute cartoon tree, thick dark-navy outline, flat bright colors, plain white background, friendly smile, no text</t>
-  </si>
-  <si>
-    <t>Payung</t>
-  </si>
-  <si>
-    <t>Van</t>
-  </si>
-  <si>
-    <t>Mobil van</t>
-  </si>
-  <si>
-    <t>cute cartoon van, thick dark-navy outline, flat bright colors, plain white background, friendly smile, no text</t>
   </si>
   <si>
     <t>cute cartoon wool, thick dark-navy outline, flat bright colors, plain white background, friendly smile, no text</t>
@@ -795,7 +825,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -820,13 +850,6 @@
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1282,148 +1305,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2590,7 +2613,7 @@
         <v>181</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>80</v>
+        <v>182</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>182</v>
@@ -2630,19 +2653,19 @@
         <v>175</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E5" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>190</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -2650,16 +2673,16 @@
         <v>29</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>194</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>8</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>195</v>
@@ -2718,10 +2741,10 @@
         <v>9</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>8</v>
+        <v>198</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>11</v>
@@ -2769,10 +2792,10 @@
         <v>37</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>36</v>
+        <v>200</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>38</v>
@@ -2786,13 +2809,13 @@
         <v>56</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>178</v>
+        <v>55</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2806,7 +2829,7 @@
         <v>14</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>17</v>
@@ -2817,16 +2840,16 @@
         <v>39</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2837,10 +2860,10 @@
         <v>61</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>80</v>
+        <v>208</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>182</v>
+        <v>209</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>81</v>
@@ -2854,10 +2877,10 @@
         <v>26</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>25</v>
+        <v>210</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>28</v>
@@ -2868,16 +2891,16 @@
         <v>53</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2885,16 +2908,16 @@
         <v>58</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>212</v>
+        <v>179</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2902,16 +2925,16 @@
         <v>63</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2919,16 +2942,16 @@
         <v>68</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>185</v>
+        <v>222</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>186</v>
+        <v>223</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2936,16 +2959,16 @@
         <v>73</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -2959,7 +2982,7 @@
         <v>65</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>67</v>
@@ -2976,7 +2999,7 @@
         <v>136</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>224</v>
+        <v>189</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>137</v>
@@ -2993,7 +3016,7 @@
         <v>93</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>96</v>
@@ -3010,7 +3033,7 @@
         <v>70</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>72</v>
@@ -3027,7 +3050,7 @@
         <v>46</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>188</v>
+        <v>232</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>47</v>
@@ -3038,16 +3061,16 @@
         <v>101</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>194</v>
+        <v>235</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -3061,7 +3084,7 @@
         <v>88</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>90</v>
@@ -3075,13 +3098,13 @@
         <v>112</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -3092,13 +3115,13 @@
         <v>32</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>189</v>
+        <v>241</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>190</v>
+        <v>242</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -3112,7 +3135,7 @@
         <v>120</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>122</v>
@@ -3129,7 +3152,7 @@
         <v>125</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>128</v>
@@ -3170,10 +3193,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -3181,7 +3204,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3189,23 +3212,23 @@
         <v>170</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -3213,31 +3236,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="B8" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="B9" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>
